--- a/results/ref_threshold_sensitivity/tables/SumRel_rda_terms_summary.xlsx
+++ b/results/ref_threshold_sensitivity/tables/SumRel_rda_terms_summary.xlsx
@@ -475,10 +475,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>251.2</v>
+        <v>293.39</v>
       </c>
       <c r="D2" t="n">
-        <v>10.03</v>
+        <v>12.47</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -489,10 +489,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="3">
@@ -505,24 +505,24 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>73.17</v>
+        <v>80.7</v>
       </c>
       <c r="D3" t="n">
-        <v>2.92</v>
+        <v>3.43</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>**</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="4">
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>39.23</v>
+        <v>32.35</v>
       </c>
       <c r="D4" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="E4" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="5">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19.69</v>
+        <v>20.04</v>
       </c>
       <c r="D5" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="E5" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-0.37</v>
+        <v>-0.42</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="6">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13.56</v>
+        <v>18.14</v>
       </c>
       <c r="D6" t="n">
-        <v>0.54</v>
+        <v>0.77</v>
       </c>
       <c r="E6" t="n">
-        <v>0.79</v>
+        <v>0.57</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="H6" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>

--- a/results/ref_threshold_sensitivity/tables/SumRel_rda_terms_summary.xlsx
+++ b/results/ref_threshold_sensitivity/tables/SumRel_rda_terms_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/results/ref_threshold_sensitivity/tables/SumRel_rda_terms_summary.xlsx
+++ b/results/ref_threshold_sensitivity/tables/SumRel_rda_terms_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,14 +471,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Measured Depth (m)</t>
+          <t>MPS (Phi)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>293.39</v>
+        <v>126.56</v>
       </c>
       <c r="D2" t="n">
-        <v>12.47</v>
+        <v>6.19</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -489,10 +489,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.89</v>
+        <v>-0.77</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.02</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="3">
@@ -501,28 +501,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Water DO Bottom (mg/L)</t>
+          <t>Measured Depth (m)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>80.7</v>
+        <v>39.72</v>
       </c>
       <c r="D3" t="n">
-        <v>3.43</v>
+        <v>1.94</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>*</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.03</v>
+        <v>0.31</v>
       </c>
       <c r="H3" t="n">
-        <v>0.47</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="4">
@@ -531,17 +531,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>Water DO Bottom (mg/L)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32.35</v>
+        <v>39.67</v>
       </c>
       <c r="D4" t="n">
-        <v>1.37</v>
+        <v>1.94</v>
       </c>
       <c r="E4" t="n">
-        <v>0.19</v>
+        <v>0.05</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-0.05</v>
+        <v>-0.26</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="5">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.04</v>
+        <v>26.02</v>
       </c>
       <c r="D5" t="n">
-        <v>0.85</v>
+        <v>1.27</v>
       </c>
       <c r="E5" t="n">
-        <v>0.53</v>
+        <v>0.24</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-0.42</v>
+        <v>0.19</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.04</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="6">
@@ -591,17 +591,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MPS (Phi)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.14</v>
+        <v>21.74</v>
       </c>
       <c r="D6" t="n">
-        <v>0.77</v>
+        <v>1.06</v>
       </c>
       <c r="E6" t="n">
-        <v>0.57</v>
+        <v>0.38</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-0.46</v>
+        <v>0.24</v>
       </c>
       <c r="H6" t="n">
-        <v>0.57</v>
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
